--- a/artfynd/A 44469-2022 artfynd.xlsx
+++ b/artfynd/A 44469-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44469-2022 artfynd.xlsx
+++ b/artfynd/A 44469-2022 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6954466</v>
+        <v>6954468</v>
       </c>
       <c r="B2" t="n">
-        <v>90671</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4368</v>
+        <v>150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>425900.4289296145</v>
+        <v>425900</v>
       </c>
       <c r="R2" t="n">
-        <v>6614350.577267532</v>
+        <v>6614351</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -758,19 +753,14 @@
           <t>2013-09-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-09-19</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>det. Tony Svensson, Mikael Hagström</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,15 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6954525</v>
+        <v>112395204</v>
       </c>
       <c r="B3" t="n">
-        <v>95514</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,36 +804,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224361</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig lopplummer</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Huperzia selago subsp. selago</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sjöändan, 350 m NV, Vrm</t>
+          <t>Sjöändan, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>425740.764862506</v>
+        <v>425634</v>
       </c>
       <c r="R3" t="n">
-        <v>6614265.289754707</v>
+        <v>6614497</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,22 +858,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-09-19</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-09-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,63 +874,53 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Ängsgranskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Crister Albinsson</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Crister Albinsson</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6954468</v>
+        <v>6954520</v>
       </c>
       <c r="B4" t="n">
-        <v>90642</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>150</v>
+        <v>4363</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -969,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>425900.4289296145</v>
+        <v>425900</v>
       </c>
       <c r="R4" t="n">
-        <v>6614350.577267532</v>
+        <v>6614351</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1002,24 +968,9 @@
           <t>2013-09-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2013-09-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>det. Tony Svensson, Mikael Hagström</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1055,16 +1006,11 @@
         <v>6954522</v>
       </c>
       <c r="B5" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1102,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>425900.4289296145</v>
+        <v>425900</v>
       </c>
       <c r="R5" t="n">
-        <v>6614350.577267532</v>
+        <v>6614351</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1135,19 +1081,9 @@
           <t>2013-09-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2013-09-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1180,42 +1116,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6954520</v>
+        <v>6954466</v>
       </c>
       <c r="B6" t="n">
-        <v>90649</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4363</v>
+        <v>4368</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1230,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>425900.4289296145</v>
+        <v>425900</v>
       </c>
       <c r="R6" t="n">
-        <v>6614350.577267532</v>
+        <v>6614351</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1263,19 +1194,9 @@
           <t>2013-09-19</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2013-09-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1311,16 +1232,11 @@
         <v>6954467</v>
       </c>
       <c r="B7" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1333,12 +1249,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1358,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>425900.4289296145</v>
+        <v>425900</v>
       </c>
       <c r="R7" t="n">
-        <v>6614350.577267532</v>
+        <v>6614351</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1391,19 +1307,9 @@
           <t>2013-09-19</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2013-09-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1436,63 +1342,51 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6954524</v>
+        <v>112395203</v>
       </c>
       <c r="B8" t="n">
-        <v>88933</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>256335</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sjöändan, 325 m NNV, Vrm</t>
+          <t>Sjöändan, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>425900.4289296145</v>
+        <v>425884</v>
       </c>
       <c r="R8" t="n">
-        <v>6614350.577267532</v>
+        <v>6614337</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1516,27 +1410,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2013-09-19</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2013-09-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>det. Mikael Hagström, Johan Nitare</t>
+          <t>2023-08-24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1549,35 +1428,25 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Gammal granskog</t>
-        </is>
-      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Crister Albinsson</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Crister Albinsson</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112395204</v>
+        <v>6954525</v>
       </c>
       <c r="B9" t="n">
-        <v>89431</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1585,37 +1454,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3215</v>
+        <v>224361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sjöändan, Vrm</t>
+          <t>Sjöändan, 350 m NV, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>425634</v>
+        <v>425741</v>
       </c>
       <c r="R9" t="n">
-        <v>6614497</v>
+        <v>6614265</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1639,12 +1511,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
+          <t>2013-09-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
+          <t>2013-09-19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1655,72 +1527,79 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Ängsgranskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Crister Albinsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Crister Albinsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112395203</v>
+        <v>6954524</v>
       </c>
       <c r="B10" t="n">
-        <v>90935</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91420</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>256335</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sjöändan, Vrm</t>
+          <t>Sjöändan, 325 m NNV, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>425883</v>
+        <v>425900</v>
       </c>
       <c r="R10" t="n">
-        <v>6614337</v>
+        <v>6614351</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1744,12 +1623,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
+          <t>2013-09-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
+          <t>2013-09-19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>det. Mikael Hagström, Johan Nitare</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1762,15 +1646,20 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Gammal granskog</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Crister Albinsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Crister Albinsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 44469-2022 artfynd.xlsx
+++ b/artfynd/A 44469-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6954468</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112395204</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6954520</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,6 +1133,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6954522</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1226,6 +1251,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6954466</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1339,6 +1369,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6954467</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1440,6 +1475,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112395203</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1545,6 +1585,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6954525</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1663,8 +1708,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6954524</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>